--- a/ig/nr-INS-Patient/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
+++ b/ig/nr-INS-Patient/StructureDefinition-fr-core-medication-administration-inhaled-oxygen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1997" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2330" uniqueCount="432">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-16T12:02:48+00:00</t>
+    <t>2023-10-16T13:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -198,13 +198,209 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>MedicationAdministration.implicitRules</t>
+    <t>MedicationAdministration.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the canonical url value</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.meta.profile:fr-canonical</t>
+  </si>
+  <si>
+    <t>fr-canonical</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>MedicationAdministration.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -215,9 +411,6 @@
   </si>
   <si>
     <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>n/a</t>
   </si>
   <si>
     <t>MedicationAdministration.language</t>
@@ -300,38 +493,10 @@
     <t>MedicationAdministration.extension</t>
   </si>
   <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationAdministration.modifierExtension</t>
@@ -471,9 +636,6 @@
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>A set of codes indicating the reason why the MedicationAdministration is negated.</t>
   </si>
   <si>
@@ -543,33 +705,10 @@
     <t>MedicationAdministration.medication[x].id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>MedicationAdministration.medication[x].extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>MedicationAdministration.medication[x].coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
   </si>
   <si>
     <t>Code defined by a terminology system</t>
@@ -1516,11 +1655,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO53"/>
+  <dimension ref="A1:AO62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="57.0859375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="57.0859375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.83203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="6" max="6" width="2.2109375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
@@ -1539,18 +1679,17 @@
     <col min="21" max="21" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="9.6640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.42578125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="58.77734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="10.26171875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="12.34765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="5.62109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="45.6171875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="2.2109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" hidden="true" width="8.0" customWidth="false"/>
     <col min="17" max="17" width="20.703125" customWidth="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="24.18359375" customWidth="true" bestFit="true"/>
@@ -1929,10 +2068,10 @@
         <v>34</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s" s="2">
         <v>60</v>
@@ -1943,9 +2082,7 @@
       <c r="M4" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="N4" t="s" s="2">
-        <v>63</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>34</v>
@@ -1994,7 +2131,7 @@
         <v>34</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>35</v>
@@ -2003,16 +2140,16 @@
         <v>44</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>34</v>
@@ -2026,21 +2163,21 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>34</v>
@@ -2087,28 +2224,28 @@
         <v>34</v>
       </c>
       <c r="X5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB5" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Y5" t="s" s="2">
+      <c r="AC5" t="s" s="2">
         <v>72</v>
       </c>
-      <c r="Z5" t="s" s="2">
+      <c r="AD5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE5" t="s" s="2">
         <v>73</v>
-      </c>
-      <c r="AA5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AB5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AC5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AD5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AE5" t="s" s="2">
-        <v>34</v>
       </c>
       <c r="AF5" t="s" s="2">
         <v>74</v>
@@ -2117,19 +2254,19 @@
         <v>35</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>34</v>
@@ -2143,14 +2280,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2166,19 +2303,19 @@
         <v>34</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>79</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2228,7 +2365,7 @@
         <v>34</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>35</v>
@@ -2246,7 +2383,7 @@
         <v>34</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>34</v>
@@ -2260,21 +2397,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>34</v>
@@ -2283,19 +2420,19 @@
         <v>34</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>88</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2345,25 +2482,25 @@
         <v>34</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>34</v>
@@ -2377,21 +2514,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>34</v>
@@ -2400,19 +2537,19 @@
         <v>34</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2450,37 +2587,37 @@
         <v>34</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="AD8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>34</v>
@@ -2494,14 +2631,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2514,26 +2651,24 @@
         <v>34</v>
       </c>
       <c r="I9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J9" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="J9" t="s" s="2">
-        <v>34</v>
-      </c>
       <c r="K9" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>34</v>
       </c>
@@ -2569,19 +2704,19 @@
         <v>34</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>35</v>
@@ -2593,13 +2728,13 @@
         <v>56</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>34</v>
@@ -2613,12 +2748,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="D10" t="s" s="2">
         <v>34</v>
       </c>
@@ -2627,7 +2764,7 @@
         <v>35</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>34</v>
@@ -2636,19 +2773,19 @@
         <v>34</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2659,7 +2796,7 @@
         <v>34</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>34</v>
@@ -2698,7 +2835,7 @@
         <v>34</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>35</v>
@@ -2713,16 +2850,16 @@
         <v>57</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>111</v>
+        <v>34</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>34</v>
@@ -2730,10 +2867,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2756,16 +2893,16 @@
         <v>45</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2791,13 +2928,13 @@
         <v>34</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>34</v>
@@ -2815,7 +2952,7 @@
         <v>34</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>35</v>
@@ -2830,16 +2967,16 @@
         <v>57</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>119</v>
+        <v>34</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>34</v>
@@ -2847,10 +2984,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2873,16 +3010,16 @@
         <v>45</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2908,13 +3045,13 @@
         <v>34</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>34</v>
+        <v>119</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>34</v>
@@ -2944,19 +3081,19 @@
         <v>56</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>34</v>
@@ -2964,10 +3101,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2975,7 +3112,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>44</v>
@@ -2990,16 +3127,16 @@
         <v>45</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3025,13 +3162,13 @@
         <v>34</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>134</v>
+        <v>34</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>34</v>
@@ -3049,10 +3186,10 @@
         <v>34</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>44</v>
@@ -3064,16 +3201,16 @@
         <v>57</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>138</v>
+        <v>34</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>34</v>
@@ -3081,10 +3218,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3095,7 +3232,7 @@
         <v>35</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>34</v>
@@ -3107,16 +3244,16 @@
         <v>34</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3142,13 +3279,13 @@
         <v>34</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>34</v>
@@ -3166,13 +3303,13 @@
         <v>34</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>56</v>
@@ -3181,16 +3318,16 @@
         <v>57</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>34</v>
@@ -3198,14 +3335,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>34</v>
+        <v>137</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3224,16 +3361,16 @@
         <v>34</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3259,13 +3396,13 @@
         <v>34</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>154</v>
+        <v>34</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>155</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>34</v>
@@ -3283,7 +3420,7 @@
         <v>34</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>35</v>
@@ -3301,13 +3438,13 @@
         <v>34</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>157</v>
+        <v>34</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>34</v>
@@ -3315,21 +3452,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>34</v>
@@ -3338,19 +3475,19 @@
         <v>34</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3376,13 +3513,13 @@
         <v>34</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>162</v>
+        <v>34</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>163</v>
+        <v>34</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>34</v>
@@ -3400,31 +3537,31 @@
         <v>34</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>164</v>
+        <v>34</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>166</v>
+        <v>34</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>167</v>
+        <v>34</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>34</v>
@@ -3432,21 +3569,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>34</v>
@@ -3458,15 +3595,17 @@
         <v>34</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>152</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>70</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>34</v>
@@ -3503,37 +3642,37 @@
         <v>34</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>34</v>
@@ -3547,14 +3686,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3567,24 +3706,26 @@
         <v>34</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>34</v>
       </c>
@@ -3620,19 +3761,19 @@
         <v>34</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>35</v>
@@ -3644,7 +3785,7 @@
         <v>56</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>34</v>
@@ -3664,10 +3805,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3675,10 +3816,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>34</v>
@@ -3687,23 +3828,21 @@
         <v>34</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>34</v>
       </c>
@@ -3751,7 +3890,7 @@
         <v>34</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>35</v>
@@ -3766,16 +3905,16 @@
         <v>57</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>34</v>
+        <v>164</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>34</v>
+        <v>166</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>34</v>
@@ -3783,10 +3922,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3797,7 +3936,7 @@
         <v>35</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>34</v>
@@ -3806,18 +3945,20 @@
         <v>34</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>34</v>
@@ -3866,25 +4007,25 @@
         <v>34</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK20" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AG20" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>34</v>
-      </c>
       <c r="AL20" t="s" s="2">
-        <v>65</v>
+        <v>173</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>34</v>
@@ -3898,14 +4039,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3921,19 +4062,19 @@
         <v>34</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3971,19 +4112,19 @@
         <v>34</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>35</v>
@@ -3995,13 +4136,13 @@
         <v>56</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>34</v>
@@ -4015,10 +4156,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4035,32 +4176,30 @@
         <v>34</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>45</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>192</v>
+        <v>34</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>34</v>
@@ -4078,13 +4217,13 @@
         <v>34</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>34</v>
+        <v>186</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>34</v>
+        <v>187</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>34</v>
@@ -4102,10 +4241,10 @@
         <v>34</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>44</v>
@@ -4117,16 +4256,16 @@
         <v>57</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>34</v>
+        <v>189</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>34</v>
+        <v>191</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>34</v>
@@ -4134,10 +4273,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4148,7 +4287,7 @@
         <v>35</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>34</v>
@@ -4157,19 +4296,19 @@
         <v>34</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>197</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4195,13 +4334,13 @@
         <v>34</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>34</v>
+        <v>198</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>34</v>
+        <v>199</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>34</v>
@@ -4219,13 +4358,13 @@
         <v>34</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>56</v>
@@ -4234,7 +4373,7 @@
         <v>57</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>201</v>
@@ -4262,7 +4401,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>44</v>
@@ -4274,10 +4413,10 @@
         <v>34</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>67</v>
+        <v>194</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>204</v>
@@ -4286,17 +4425,15 @@
         <v>205</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>34</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>208</v>
+        <v>34</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>34</v>
@@ -4314,13 +4451,13 @@
         <v>34</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>34</v>
+        <v>207</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>34</v>
@@ -4338,7 +4475,7 @@
         <v>34</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>35</v>
@@ -4356,13 +4493,13 @@
         <v>34</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>34</v>
@@ -4370,10 +4507,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4381,7 +4518,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>44</v>
@@ -4396,20 +4533,18 @@
         <v>45</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>215</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>34</v>
       </c>
@@ -4433,13 +4568,13 @@
         <v>34</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>34</v>
+        <v>214</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>34</v>
+        <v>215</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>34</v>
@@ -4457,10 +4592,10 @@
         <v>34</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>44</v>
@@ -4472,16 +4607,16 @@
         <v>57</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>217</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>34</v>
+        <v>218</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>34</v>
@@ -4489,10 +4624,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4512,23 +4647,19 @@
         <v>34</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>221</v>
+        <v>61</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>34</v>
       </c>
@@ -4576,7 +4707,7 @@
         <v>34</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>225</v>
+        <v>63</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>35</v>
@@ -4585,22 +4716,22 @@
         <v>44</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>227</v>
+        <v>34</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>34</v>
@@ -4608,21 +4739,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>34</v>
@@ -4631,23 +4762,21 @@
         <v>34</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>229</v>
+        <v>68</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>230</v>
+        <v>69</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>34</v>
       </c>
@@ -4683,43 +4812,43 @@
         <v>34</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>233</v>
+        <v>74</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>234</v>
+        <v>58</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>235</v>
+        <v>34</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>34</v>
@@ -4727,10 +4856,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4753,18 +4882,20 @@
         <v>45</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>237</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>34</v>
       </c>
@@ -4812,31 +4943,31 @@
         <v>34</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>240</v>
+        <v>34</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>242</v>
+        <v>34</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>34</v>
@@ -4844,10 +4975,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4870,17 +5001,15 @@
         <v>34</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>245</v>
+        <v>60</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>246</v>
+        <v>61</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>125</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>34</v>
@@ -4929,7 +5058,7 @@
         <v>34</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>244</v>
+        <v>63</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>35</v>
@@ -4938,22 +5067,22 @@
         <v>44</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>126</v>
+        <v>34</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>248</v>
+        <v>34</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>249</v>
+        <v>64</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>251</v>
+        <v>34</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>34</v>
@@ -4961,14 +5090,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -4987,16 +5116,16 @@
         <v>34</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>253</v>
+        <v>67</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>254</v>
+        <v>68</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>255</v>
+        <v>69</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5034,19 +5163,19 @@
         <v>34</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>252</v>
+        <v>74</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>35</v>
@@ -5058,16 +5187,16 @@
         <v>56</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>256</v>
+        <v>58</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>34</v>
@@ -5078,10 +5207,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5104,22 +5233,26 @@
         <v>45</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>258</v>
+        <v>88</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>34</v>
+        <v>237</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>34</v>
@@ -5161,10 +5294,10 @@
         <v>34</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>44</v>
@@ -5176,16 +5309,16 @@
         <v>57</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>261</v>
+        <v>34</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>263</v>
+        <v>34</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>34</v>
@@ -5193,10 +5326,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>241</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5207,7 +5340,7 @@
         <v>35</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>34</v>
@@ -5219,15 +5352,17 @@
         <v>45</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>266</v>
+        <v>60</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>244</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>34</v>
@@ -5276,13 +5411,13 @@
         <v>34</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>56</v>
@@ -5291,16 +5426,16 @@
         <v>57</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>269</v>
+        <v>34</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>271</v>
+        <v>34</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>34</v>
@@ -5308,10 +5443,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5319,7 +5454,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>44</v>
@@ -5331,25 +5466,29 @@
         <v>34</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>170</v>
+        <v>249</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>34</v>
@@ -5391,7 +5530,7 @@
         <v>34</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>172</v>
+        <v>254</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>35</v>
@@ -5400,22 +5539,22 @@
         <v>44</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>65</v>
+        <v>255</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>34</v>
+        <v>256</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>34</v>
@@ -5423,21 +5562,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>34</v>
@@ -5446,21 +5585,23 @@
         <v>34</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>93</v>
+        <v>258</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>174</v>
+        <v>259</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>34</v>
       </c>
@@ -5496,43 +5637,43 @@
         <v>34</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>175</v>
+        <v>261</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>58</v>
+        <v>262</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>34</v>
+        <v>263</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>34</v>
@@ -5540,45 +5681,45 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>45</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>92</v>
+        <v>265</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>95</v>
+        <v>268</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>104</v>
+        <v>269</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>34</v>
@@ -5627,31 +5768,31 @@
         <v>34</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>58</v>
+        <v>271</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>34</v>
+        <v>272</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>34</v>
@@ -5659,10 +5800,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5682,21 +5823,23 @@
         <v>34</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>34</v>
       </c>
@@ -5720,13 +5863,13 @@
         <v>34</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>283</v>
+        <v>34</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>284</v>
+        <v>34</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>34</v>
@@ -5744,7 +5887,7 @@
         <v>34</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>35</v>
@@ -5759,16 +5902,16 @@
         <v>57</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>285</v>
+        <v>34</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>157</v>
+        <v>280</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>34</v>
@@ -5776,10 +5919,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5802,16 +5945,16 @@
         <v>45</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5861,7 +6004,7 @@
         <v>34</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>44</v>
@@ -5873,19 +6016,19 @@
         <v>56</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>34</v>
+        <v>287</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>34</v>
+        <v>288</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>34</v>
@@ -5893,10 +6036,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5907,7 +6050,7 @@
         <v>35</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>34</v>
@@ -5919,16 +6062,16 @@
         <v>34</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>141</v>
+        <v>290</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5954,13 +6097,13 @@
         <v>34</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>296</v>
+        <v>34</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>297</v>
+        <v>34</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>34</v>
@@ -5978,31 +6121,31 @@
         <v>34</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>34</v>
+        <v>295</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>34</v>
@@ -6010,10 +6153,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6036,16 +6179,16 @@
         <v>34</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>305</v>
+        <v>178</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6095,7 +6238,7 @@
         <v>34</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>35</v>
@@ -6107,30 +6250,30 @@
         <v>56</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>126</v>
+        <v>179</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>306</v>
+        <v>34</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>309</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6138,7 +6281,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>44</v>
@@ -6150,20 +6293,18 @@
         <v>34</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>34</v>
@@ -6212,10 +6353,10 @@
         <v>34</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>44</v>
@@ -6224,19 +6365,19 @@
         <v>56</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>34</v>
+        <v>308</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>34</v>
@@ -6244,10 +6385,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6267,20 +6408,18 @@
         <v>34</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>125</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>34</v>
@@ -6329,7 +6468,7 @@
         <v>34</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>35</v>
@@ -6341,19 +6480,19 @@
         <v>56</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>34</v>
+        <v>314</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>34</v>
+        <v>316</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>34</v>
@@ -6361,10 +6500,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6375,7 +6514,7 @@
         <v>35</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>34</v>
@@ -6387,17 +6526,15 @@
         <v>34</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>325</v>
+        <v>60</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>326</v>
+        <v>61</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>34</v>
@@ -6446,31 +6583,31 @@
         <v>34</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>324</v>
+        <v>63</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>329</v>
+        <v>34</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>330</v>
+        <v>64</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>34</v>
@@ -6478,21 +6615,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>34</v>
@@ -6504,15 +6641,17 @@
         <v>34</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>266</v>
+        <v>67</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>332</v>
+        <v>68</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>70</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>34</v>
@@ -6549,37 +6688,37 @@
         <v>34</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>331</v>
+        <v>74</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>334</v>
+        <v>75</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>335</v>
+        <v>58</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>34</v>
@@ -6593,42 +6732,46 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>34</v>
+        <v>321</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>169</v>
+        <v>67</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>170</v>
+        <v>322</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>34</v>
       </c>
@@ -6676,25 +6819,25 @@
         <v>34</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>172</v>
+        <v>324</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>34</v>
@@ -6708,21 +6851,21 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>34</v>
@@ -6734,16 +6877,16 @@
         <v>34</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>92</v>
+        <v>194</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>93</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>174</v>
+        <v>327</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6769,55 +6912,55 @@
         <v>34</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>34</v>
+        <v>328</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>34</v>
+        <v>329</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>34</v>
+        <v>330</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>58</v>
+        <v>331</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>34</v>
+        <v>209</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>34</v>
@@ -6825,46 +6968,44 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>34</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>45</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>92</v>
+        <v>333</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>277</v>
+        <v>334</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>34</v>
       </c>
@@ -6912,25 +7053,25 @@
         <v>34</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>34</v>
+        <v>336</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>58</v>
+        <v>337</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>34</v>
@@ -6944,10 +7085,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6958,7 +7099,7 @@
         <v>35</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>34</v>
@@ -6970,16 +7111,16 @@
         <v>34</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M47" t="s" s="2">
-        <v>341</v>
-      </c>
       <c r="N47" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7005,13 +7146,13 @@
         <v>34</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>34</v>
+        <v>118</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>34</v>
+        <v>341</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>34</v>
+        <v>342</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>34</v>
@@ -7029,13 +7170,13 @@
         <v>34</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>56</v>
@@ -7044,16 +7185,16 @@
         <v>57</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>34</v>
+        <v>343</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>34</v>
+        <v>345</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>34</v>
@@ -7061,10 +7202,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7075,7 +7216,7 @@
         <v>35</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>34</v>
@@ -7087,16 +7228,16 @@
         <v>34</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>141</v>
+        <v>347</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7122,13 +7263,13 @@
         <v>34</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>347</v>
+        <v>34</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>348</v>
+        <v>34</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>34</v>
@@ -7146,42 +7287,42 @@
         <v>34</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>34</v>
+        <v>351</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>34</v>
+        <v>353</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>34</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7204,16 +7345,16 @@
         <v>34</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>141</v>
+        <v>356</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>144</v>
+        <v>359</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7239,31 +7380,31 @@
         <v>34</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>354</v>
+        <v>34</v>
       </c>
       <c r="Z49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF49" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AA49" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AB49" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AD49" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>35</v>
@@ -7275,19 +7416,19 @@
         <v>56</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>34</v>
+        <v>360</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>34</v>
@@ -7295,10 +7436,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7309,7 +7450,7 @@
         <v>35</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>34</v>
@@ -7321,16 +7462,16 @@
         <v>34</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>141</v>
+        <v>364</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>361</v>
+        <v>178</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7356,55 +7497,55 @@
         <v>34</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>145</v>
+        <v>34</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>362</v>
+        <v>34</v>
       </c>
       <c r="Z50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AA50" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="AG50" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>57</v>
+        <v>179</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>34</v>
@@ -7412,10 +7553,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7426,7 +7567,7 @@
         <v>35</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>34</v>
@@ -7438,16 +7579,16 @@
         <v>34</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7497,31 +7638,31 @@
         <v>34</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>56</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>371</v>
+        <v>57</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>34</v>
+        <v>374</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>373</v>
+        <v>58</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>34</v>
@@ -7529,10 +7670,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7555,17 +7696,15 @@
         <v>34</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>375</v>
+        <v>311</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N52" t="s" s="2">
         <v>378</v>
       </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>34</v>
@@ -7614,7 +7753,7 @@
         <v>34</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>35</v>
@@ -7626,19 +7765,19 @@
         <v>56</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>57</v>
+        <v>379</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>380</v>
+        <v>34</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>34</v>
@@ -7660,7 +7799,7 @@
         <v>35</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>34</v>
@@ -7672,17 +7811,15 @@
         <v>34</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>382</v>
+        <v>60</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>383</v>
+        <v>61</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>34</v>
@@ -7731,33 +7868,1088 @@
         <v>34</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>63</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH53" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G54" t="s" s="2">
         <v>36</v>
       </c>
-      <c r="AI53" t="s" s="2">
+      <c r="H54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI54" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="AJ53" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AJ54" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AM53" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AO53" t="s" s="2">
+      <c r="N56" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AO62" t="s" s="2">
         <v>34</v>
       </c>
     </row>
